--- a/data/raw/Сash_Flow_Actual.xlsx
+++ b/data/raw/Сash_Flow_Actual.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="13" yWindow="100" windowWidth="24242" windowHeight="15151" tabRatio="924" firstSheet="1" activeTab="8"/>
+    <workbookView xWindow="13" yWindow="100" windowWidth="24242" windowHeight="15151" tabRatio="924" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Cash Flow Statement_Actual" sheetId="1" r:id="rId1"/>
